--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260703_205418.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260703_205418.xlsx
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260703_205418.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260703_205418.xlsx
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260703_205418.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260703_205418.xlsx
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
